--- a/salidas/empresas/PLD.xlsx
+++ b/salidas/empresas/PLD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>26.47858810424805</v>
+        <v>26.47859001159668</v>
       </c>
       <c r="C2" t="n">
         <v>52.20000076293945</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>27.21410179138184</v>
+        <v>27.21410751342773</v>
       </c>
       <c r="C3" t="n">
         <v>53.65000152587891</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>27.52860832214355</v>
+        <v>27.52859878540039</v>
       </c>
       <c r="C4" t="n">
         <v>54.27000045776367</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>25.58007431030273</v>
+        <v>25.58008003234863</v>
       </c>
       <c r="C5" t="n">
         <v>49.9900016784668</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>25.29351997375488</v>
+        <v>25.29351806640625</v>
       </c>
       <c r="C6" t="n">
         <v>49.43000030517578</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>25.86662864685059</v>
+        <v>25.86663055419922</v>
       </c>
       <c r="C7" t="n">
         <v>50.54999923706055</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>27.07033157348633</v>
+        <v>27.07032775878906</v>
       </c>
       <c r="C8" t="n">
         <v>52.43000030517578</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>28.8257999420166</v>
+        <v>28.82579040527344</v>
       </c>
       <c r="C9" t="n">
         <v>55.83000183105469</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>28.45405197143555</v>
+        <v>28.45404052734375</v>
       </c>
       <c r="C10" t="n">
         <v>55.11000061035156</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>30.40579795837402</v>
+        <v>30.4057788848877</v>
       </c>
       <c r="C11" t="n">
         <v>58.40999984741211</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>31.89458274841309</v>
+        <v>31.89458656311035</v>
       </c>
       <c r="C12" t="n">
         <v>61.27000045776367</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>30.7480297088623</v>
+        <v>30.74802589416504</v>
       </c>
       <c r="C13" t="n">
         <v>58.61000061035156</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>31.92317390441895</v>
+        <v>31.92317581176758</v>
       </c>
       <c r="C14" t="n">
         <v>60.84999847412109</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>30.84771728515625</v>
+        <v>30.84770011901855</v>
       </c>
       <c r="C15" t="n">
         <v>58.79999923706055</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>32.2255859375</v>
+        <v>32.2255973815918</v>
       </c>
       <c r="C17" t="n">
         <v>60.90999984741211</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>28.15704345703125</v>
+        <v>28.15703392028809</v>
       </c>
       <c r="C19" t="n">
         <v>53.22000122070312</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>28.44366645812988</v>
+        <v>28.44366264343262</v>
       </c>
       <c r="C20" t="n">
         <v>53.27999877929688</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>29.35122108459473</v>
+        <v>29.35121726989746</v>
       </c>
       <c r="C21" t="n">
         <v>54.97999954223633</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>31.92972946166992</v>
+        <v>31.9297046661377</v>
       </c>
       <c r="C22" t="n">
         <v>59.81000137329102</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>35.16738891601562</v>
+        <v>35.16736221313477</v>
       </c>
       <c r="C23" t="n">
         <v>65.34999847412109</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>32.91258239746094</v>
+        <v>32.91257858276367</v>
       </c>
       <c r="C24" t="n">
         <v>61.15999984741211</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>31.25693893432617</v>
+        <v>31.25691986083984</v>
       </c>
       <c r="C25" t="n">
         <v>57.56000137329102</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>27.46113204956055</v>
+        <v>27.46112632751465</v>
       </c>
       <c r="C26" t="n">
         <v>50.56999969482422</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>27.24936485290527</v>
+        <v>27.24935340881348</v>
       </c>
       <c r="C27" t="n">
         <v>50.18000030517578</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>29.55181312561035</v>
+        <v>29.55180740356445</v>
       </c>
       <c r="C28" t="n">
         <v>54.41999816894531</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>31.647705078125</v>
+        <v>31.64771270751953</v>
       </c>
       <c r="C29" t="n">
         <v>57.75</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>32.29983520507812</v>
+        <v>32.29985046386719</v>
       </c>
       <c r="C30" t="n">
         <v>58.93999862670898</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>27.60887145996094</v>
+        <v>27.60885810852051</v>
       </c>
       <c r="C31" t="n">
         <v>50.38000106811523</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>27.11050796508789</v>
+        <v>27.11051177978516</v>
       </c>
       <c r="C32" t="n">
         <v>48.95999908447266</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>25.13369750976562</v>
+        <v>25.13369369506836</v>
       </c>
       <c r="C33" t="n">
         <v>45.38999938964844</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>25.0838680267334</v>
+        <v>25.08386039733887</v>
       </c>
       <c r="C34" t="n">
         <v>45.29999923706055</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>13.46736335754395</v>
+        <v>13.46736431121826</v>
       </c>
       <c r="C35" t="n">
         <v>24.03000068664551</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>9.650768280029297</v>
+        <v>9.650769233703613</v>
       </c>
       <c r="C36" t="n">
         <v>17.21999931335449</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>13.12549591064453</v>
+        <v>13.12549686431885</v>
       </c>
       <c r="C37" t="n">
         <v>23.42000007629395</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>9.034284591674805</v>
+        <v>9.034285545349121</v>
       </c>
       <c r="C38" t="n">
         <v>16.1200008392334</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>6.674831867218018</v>
+        <v>6.674835681915283</v>
       </c>
       <c r="C39" t="n">
         <v>11.90999984741211</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>8.070328712463379</v>
+        <v>8.070331573486328</v>
       </c>
       <c r="C40" t="n">
         <v>14.39999961853027</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>10.90725898742676</v>
+        <v>10.90725708007812</v>
       </c>
       <c r="C41" t="n">
         <v>19.09000015258789</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>10.19877052307129</v>
+        <v>10.19876766204834</v>
       </c>
       <c r="C42" t="n">
         <v>17.85000038146973</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.74727630615234</v>
+        <v>10.74727725982666</v>
       </c>
       <c r="C43" t="n">
         <v>18.80999946594238</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>11.48966217041016</v>
+        <v>11.48966789245605</v>
       </c>
       <c r="C44" t="n">
         <v>19.80999946594238</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>13.24124717712402</v>
+        <v>13.24124813079834</v>
       </c>
       <c r="C45" t="n">
         <v>22.82999992370605</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>13.31085205078125</v>
+        <v>13.31085014343262</v>
       </c>
       <c r="C46" t="n">
         <v>22.95000076293945</v>
@@ -1337,7 +1349,7 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>13.82754611968994</v>
+        <v>13.82754516601562</v>
       </c>
       <c r="C48" t="n">
         <v>23.54999923706055</v>
@@ -1375,11 +1387,11 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>15.16921424865723</v>
+        <v>15.16920757293701</v>
       </c>
       <c r="C49" t="n">
         <v>25.54999923706055</v>
@@ -1394,11 +1406,11 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>14.24896621704102</v>
+        <v>14.24896717071533</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1413,11 +1425,11 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>14.45082187652588</v>
+        <v>14.45082473754883</v>
       </c>
       <c r="C51" t="n">
         <v>24.34000015258789</v>
@@ -1432,11 +1444,11 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>16.33730506896973</v>
+        <v>16.33729934692383</v>
       </c>
       <c r="C52" t="n">
         <v>27.23999977111816</v>
@@ -1451,11 +1463,11 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>16.70914268493652</v>
+        <v>16.70914459228516</v>
       </c>
       <c r="C53" t="n">
         <v>27.86000061035156</v>
@@ -1470,11 +1482,11 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>15.55161762237549</v>
+        <v>15.55162239074707</v>
       </c>
       <c r="C54" t="n">
         <v>25.93000030517578</v>
@@ -1489,11 +1501,11 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>14.22017288208008</v>
+        <v>14.22017192840576</v>
       </c>
       <c r="C55" t="n">
         <v>23.70999908447266</v>
@@ -1508,11 +1520,11 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>15.148756980896</v>
+        <v>15.14875411987305</v>
       </c>
       <c r="C56" t="n">
         <v>24.95999908447266</v>
@@ -1527,11 +1539,11 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>14.43865203857422</v>
+        <v>14.4386625289917</v>
       </c>
       <c r="C57" t="n">
         <v>23.79000091552734</v>
@@ -1552,11 +1564,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>16.06521224975586</v>
+        <v>16.06521034240723</v>
       </c>
       <c r="C58" t="n">
         <v>26.46999931335449</v>
@@ -1577,11 +1589,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>17.29203224182129</v>
+        <v>17.29203033447266</v>
       </c>
       <c r="C59" t="n">
         <v>28.19000053405762</v>
@@ -1602,11 +1614,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>17.90544319152832</v>
+        <v>17.90543365478516</v>
       </c>
       <c r="C60" t="n">
         <v>29.19000053405762</v>
@@ -1627,11 +1639,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>19.6265869140625</v>
+        <v>19.6265811920166</v>
       </c>
       <c r="C61" t="n">
         <v>31.70999908447266</v>
@@ -1652,11 +1664,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>20.76543807983398</v>
+        <v>20.76542663574219</v>
       </c>
       <c r="C62" t="n">
         <v>33.54999923706055</v>
@@ -1677,11 +1689,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>22.70574378967285</v>
+        <v>22.70574569702148</v>
       </c>
       <c r="C63" t="n">
         <v>36.38000106811523</v>
@@ -1702,11 +1714,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>22.44985961914062</v>
+        <v>22.44985198974609</v>
       </c>
       <c r="C64" t="n">
         <v>35.97000122070312</v>
@@ -1727,11 +1739,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>22.71822738647461</v>
+        <v>22.71821975708008</v>
       </c>
       <c r="C65" t="n">
         <v>36.40000152587891</v>
@@ -1752,11 +1764,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>23.26937484741211</v>
+        <v>23.26938056945801</v>
       </c>
       <c r="C66" t="n">
         <v>36.9900016784668</v>
@@ -1777,11 +1789,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>22.54593658447266</v>
+        <v>22.54594039916992</v>
       </c>
       <c r="C67" t="n">
         <v>35.84000015258789</v>
@@ -1802,11 +1814,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>22.41383171081543</v>
+        <v>22.41383361816406</v>
       </c>
       <c r="C68" t="n">
         <v>35.63000106811523</v>
@@ -1827,11 +1839,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>17.12963485717773</v>
+        <v>17.1296272277832</v>
       </c>
       <c r="C69" t="n">
         <v>27.22999954223633</v>
@@ -1852,11 +1864,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>15.41752624511719</v>
+        <v>15.41752529144287</v>
       </c>
       <c r="C70" t="n">
         <v>24.25</v>
@@ -1877,11 +1889,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>18.92064476013184</v>
+        <v>18.92065238952637</v>
       </c>
       <c r="C71" t="n">
         <v>29.76000022888184</v>
@@ -1902,11 +1914,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>17.68724632263184</v>
+        <v>17.6872444152832</v>
       </c>
       <c r="C72" t="n">
         <v>27.81999969482422</v>
@@ -1927,11 +1939,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>18.36748886108398</v>
+        <v>18.36747741699219</v>
       </c>
       <c r="C73" t="n">
         <v>28.59000015258789</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>20.37191009521484</v>
+        <v>20.37190628051758</v>
       </c>
       <c r="C74" t="n">
         <v>31.70999908447266</v>
@@ -1977,11 +1989,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>21.62467002868652</v>
+        <v>21.62467384338379</v>
       </c>
       <c r="C75" t="n">
         <v>33.65999984741211</v>
@@ -2004,11 +2016,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>23.33180999755859</v>
+        <v>23.33181190490723</v>
       </c>
       <c r="C76" t="n">
         <v>36.02000045776367</v>
@@ -2031,7 +2043,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2058,7 +2070,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2085,11 +2097,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>21.71459770202637</v>
+        <v>21.7145938873291</v>
       </c>
       <c r="C79" t="n">
         <v>33.22999954223633</v>
@@ -2112,11 +2124,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>21.12648963928223</v>
+        <v>21.12648391723633</v>
       </c>
       <c r="C80" t="n">
         <v>32.33000183105469</v>
@@ -2139,11 +2151,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>22.32884788513184</v>
+        <v>22.32884979248047</v>
       </c>
       <c r="C81" t="n">
         <v>34.16999816894531</v>
@@ -2168,11 +2180,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>23.06937026977539</v>
+        <v>23.06936454772949</v>
       </c>
       <c r="C82" t="n">
         <v>35.02999877929688</v>
@@ -2197,7 +2209,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2226,11 +2238,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>22.35153579711914</v>
+        <v>22.35153007507324</v>
       </c>
       <c r="C84" t="n">
         <v>33.93999862670898</v>
@@ -2255,11 +2267,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>24.22317886352539</v>
+        <v>24.22316741943359</v>
       </c>
       <c r="C85" t="n">
         <v>36.4900016784668</v>
@@ -2284,11 +2296,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>26.48683166503906</v>
+        <v>26.48682975769043</v>
       </c>
       <c r="C86" t="n">
         <v>39.90000152587891</v>
@@ -2313,11 +2325,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>25.84954833984375</v>
+        <v>25.84955215454102</v>
       </c>
       <c r="C87" t="n">
         <v>38.93999862670898</v>
@@ -2340,11 +2352,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>26.72964859008789</v>
+        <v>26.72965812683105</v>
       </c>
       <c r="C88" t="n">
         <v>39.97999954223633</v>
@@ -2367,11 +2379,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>28.04674339294434</v>
+        <v>28.04675102233887</v>
       </c>
       <c r="C89" t="n">
         <v>41.95000076293945</v>
@@ -2394,11 +2406,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>26.94358825683594</v>
+        <v>26.94359397888184</v>
       </c>
       <c r="C90" t="n">
         <v>40.29999923706055</v>
@@ -2421,11 +2433,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>25.39982032775879</v>
+        <v>25.39982414245605</v>
       </c>
       <c r="C91" t="n">
         <v>37.72000122070312</v>
@@ -2448,11 +2460,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>25.83078956604004</v>
+        <v>25.83078384399414</v>
       </c>
       <c r="C92" t="n">
         <v>38.36000061035156</v>
@@ -2475,11 +2487,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>23.72984504699707</v>
+        <v>23.72985076904297</v>
       </c>
       <c r="C93" t="n">
         <v>35.2400016784668</v>
@@ -2502,11 +2514,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>25.5234203338623</v>
+        <v>25.52341270446777</v>
       </c>
       <c r="C94" t="n">
         <v>37.61999893188477</v>
@@ -2529,7 +2541,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2556,11 +2568,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>25.73373222351074</v>
+        <v>25.73373794555664</v>
       </c>
       <c r="C96" t="n">
         <v>37.93000030517578</v>
@@ -2585,11 +2597,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>25.26377296447754</v>
+        <v>25.2637825012207</v>
       </c>
       <c r="C97" t="n">
         <v>36.95000076293945</v>
@@ -2614,11 +2626,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>26.50131988525391</v>
+        <v>26.5013256072998</v>
       </c>
       <c r="C98" t="n">
         <v>38.7599983215332</v>
@@ -2643,11 +2655,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>28.16278839111328</v>
+        <v>28.16277885437012</v>
       </c>
       <c r="C99" t="n">
         <v>41.18999862670898</v>
@@ -2672,11 +2684,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>28.14389991760254</v>
+        <v>28.14388275146484</v>
       </c>
       <c r="C100" t="n">
         <v>40.83000183105469</v>
@@ -2701,11 +2713,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>28.00602531433105</v>
+        <v>28.00603675842285</v>
       </c>
       <c r="C101" t="n">
         <v>40.63000106811523</v>
@@ -2730,11 +2742,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>28.61260986328125</v>
+        <v>28.61260223388672</v>
       </c>
       <c r="C102" t="n">
         <v>41.5099983215332</v>
@@ -2759,11 +2771,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>28.54638481140137</v>
+        <v>28.54639434814453</v>
       </c>
       <c r="C103" t="n">
         <v>41.09000015258789</v>
@@ -2788,11 +2800,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>28.35187149047852</v>
+        <v>28.35186767578125</v>
       </c>
       <c r="C104" t="n">
         <v>40.81000137329102</v>
@@ -2817,7 +2829,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2846,11 +2858,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>26.41482353210449</v>
+        <v>26.41481971740723</v>
       </c>
       <c r="C106" t="n">
         <v>37.70000076293945</v>
@@ -2875,7 +2887,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -2904,11 +2916,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>29.62384033203125</v>
+        <v>29.62383460998535</v>
       </c>
       <c r="C108" t="n">
         <v>42.27999877929688</v>
@@ -2933,11 +2945,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>30.38672637939453</v>
+        <v>30.3867359161377</v>
       </c>
       <c r="C109" t="n">
         <v>43.02999877929688</v>
@@ -2962,11 +2974,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>31.87676620483398</v>
+        <v>31.87676239013672</v>
       </c>
       <c r="C110" t="n">
         <v>45.13999938964844</v>
@@ -2991,11 +3003,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>30.1607494354248</v>
+        <v>30.1607551574707</v>
       </c>
       <c r="C111" t="n">
         <v>42.70999908447266</v>
@@ -3020,11 +3032,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>31.02410697937012</v>
+        <v>31.02410125732422</v>
       </c>
       <c r="C112" t="n">
         <v>43.56000137329102</v>
@@ -3049,11 +3061,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>28.63106536865234</v>
+        <v>28.63106346130371</v>
       </c>
       <c r="C113" t="n">
         <v>40.20000076293945</v>
@@ -3078,7 +3090,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3107,11 +3119,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>26.66438293457031</v>
+        <v>26.66438484191895</v>
       </c>
       <c r="C115" t="n">
         <v>37.09999847412109</v>
@@ -3136,11 +3148,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>29.18707656860352</v>
+        <v>29.18708229064941</v>
       </c>
       <c r="C116" t="n">
         <v>40.61000061035156</v>
@@ -3165,11 +3177,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>27.31122398376465</v>
+        <v>27.31122970581055</v>
       </c>
       <c r="C117" t="n">
         <v>38</v>
@@ -3194,11 +3206,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>28.25757026672363</v>
+        <v>28.25756645202637</v>
       </c>
       <c r="C118" t="n">
         <v>38.90000152587891</v>
@@ -3223,11 +3235,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>31.03974342346191</v>
+        <v>31.03973770141602</v>
       </c>
       <c r="C119" t="n">
         <v>42.72999954223633</v>
@@ -3252,11 +3264,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>31.05427169799805</v>
+        <v>31.05426979064941</v>
       </c>
       <c r="C120" t="n">
         <v>42.75</v>
@@ -3281,11 +3293,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>31.47761917114258</v>
+        <v>31.47760772705078</v>
       </c>
       <c r="C121" t="n">
         <v>42.91999816894531</v>
@@ -3310,11 +3322,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>28.9473819732666</v>
+        <v>28.9473762512207</v>
       </c>
       <c r="C122" t="n">
         <v>39.47000122070312</v>
@@ -3339,11 +3351,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>28.20663642883301</v>
+        <v>28.20663833618164</v>
       </c>
       <c r="C123" t="n">
         <v>38.45999908447266</v>
@@ -3368,11 +3380,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>32.72626113891602</v>
+        <v>32.72626495361328</v>
       </c>
       <c r="C124" t="n">
         <v>44.18000030517578</v>
@@ -3397,11 +3409,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>33.63738250732422</v>
+        <v>33.63737487792969</v>
       </c>
       <c r="C125" t="n">
         <v>45.40999984741211</v>
@@ -3426,11 +3438,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>35.207763671875</v>
+        <v>35.20777893066406</v>
       </c>
       <c r="C126" t="n">
         <v>47.52999877929688</v>
@@ -3455,11 +3467,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>36.63804244995117</v>
+        <v>36.63804626464844</v>
       </c>
       <c r="C127" t="n">
         <v>49.04000091552734</v>
@@ -3484,11 +3496,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>40.70977401733398</v>
+        <v>40.70977783203125</v>
       </c>
       <c r="C128" t="n">
         <v>54.4900016784668</v>
@@ -3513,11 +3525,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>39.67877197265625</v>
+        <v>39.67876434326172</v>
       </c>
       <c r="C129" t="n">
         <v>53.11000061035156</v>
@@ -3542,11 +3554,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>40.32891845703125</v>
+        <v>40.32892608642578</v>
       </c>
       <c r="C130" t="n">
         <v>53.54000091552734</v>
@@ -3571,11 +3583,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>39.28942489624023</v>
+        <v>39.2894287109375</v>
       </c>
       <c r="C131" t="n">
         <v>52.15999984741211</v>
@@ -3600,11 +3612,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>38.34035491943359</v>
+        <v>38.3403434753418</v>
       </c>
       <c r="C132" t="n">
         <v>50.90000152587891</v>
@@ -3629,11 +3641,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>40.08927536010742</v>
+        <v>40.08929443359375</v>
       </c>
       <c r="C133" t="n">
         <v>52.79000091552734</v>
@@ -3658,11 +3670,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>37.09720611572266</v>
+        <v>37.09720993041992</v>
       </c>
       <c r="C134" t="n">
         <v>48.84999847412109</v>
@@ -3687,11 +3699,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>38.76791763305664</v>
+        <v>38.76790618896484</v>
       </c>
       <c r="C135" t="n">
         <v>51.04999923706055</v>
@@ -3716,7 +3728,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3745,7 +3757,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3774,11 +3786,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>42.55670547485352</v>
+        <v>42.55671691894531</v>
       </c>
       <c r="C138" t="n">
         <v>55.54000091552734</v>
@@ -3803,11 +3815,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>45.28078460693359</v>
+        <v>45.2807731628418</v>
       </c>
       <c r="C139" t="n">
         <v>58.63999938964844</v>
@@ -3832,7 +3844,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3861,11 +3873,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>48.92547988891602</v>
+        <v>48.92548370361328</v>
       </c>
       <c r="C141" t="n">
         <v>63.36000061035156</v>
@@ -3890,11 +3902,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>49.33517074584961</v>
+        <v>49.33518218994141</v>
       </c>
       <c r="C142" t="n">
         <v>63.45999908447266</v>
@@ -3919,11 +3931,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>50.20589447021484</v>
+        <v>50.20589065551758</v>
       </c>
       <c r="C143" t="n">
         <v>64.58000183105469</v>
@@ -3948,7 +3960,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -3977,11 +3989,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>50.48852157592773</v>
+        <v>50.4885139465332</v>
       </c>
       <c r="C145" t="n">
         <v>64.51000213623047</v>
@@ -4006,11 +4018,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>50.95810317993164</v>
+        <v>50.95810699462891</v>
       </c>
       <c r="C146" t="n">
         <v>65.11000061035156</v>
@@ -4035,11 +4047,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>47.49098587036133</v>
+        <v>47.49098205566406</v>
       </c>
       <c r="C147" t="n">
         <v>60.68000030517578</v>
@@ -4064,11 +4076,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>49.6751708984375</v>
+        <v>49.67517471313477</v>
       </c>
       <c r="C148" t="n">
         <v>62.9900016784668</v>
@@ -4093,11 +4105,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>51.18931579589844</v>
+        <v>51.1893196105957</v>
       </c>
       <c r="C149" t="n">
         <v>64.91000366210938</v>
@@ -4122,11 +4134,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>50.7476921081543</v>
+        <v>50.74768447875977</v>
       </c>
       <c r="C150" t="n">
         <v>64.34999847412109</v>
@@ -4151,7 +4163,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4180,11 +4192,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>52.13121032714844</v>
+        <v>52.13120269775391</v>
       </c>
       <c r="C152" t="n">
         <v>65.62000274658203</v>
@@ -4209,11 +4221,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>53.37052917480469</v>
+        <v>53.37053680419922</v>
       </c>
       <c r="C153" t="n">
         <v>67.18000030517578</v>
@@ -4238,11 +4250,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>54.24033737182617</v>
+        <v>54.2403450012207</v>
       </c>
       <c r="C154" t="n">
         <v>67.79000091552734</v>
@@ -4267,11 +4279,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>51.58393859863281</v>
+        <v>51.58393478393555</v>
       </c>
       <c r="C155" t="n">
         <v>64.47000122070312</v>
@@ -4296,11 +4308,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>53.88028335571289</v>
+        <v>53.88027572631836</v>
       </c>
       <c r="C156" t="n">
         <v>67.33999633789062</v>
@@ -4325,7 +4337,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4354,11 +4366,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>55.74939727783203</v>
+        <v>55.74941253662109</v>
       </c>
       <c r="C158" t="n">
         <v>69.16000366210938</v>
@@ -4383,11 +4395,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>56.47488403320312</v>
+        <v>56.47489166259766</v>
       </c>
       <c r="C159" t="n">
         <v>70.05999755859375</v>
@@ -4412,11 +4424,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>58.42623519897461</v>
+        <v>58.42621612548828</v>
       </c>
       <c r="C160" t="n">
         <v>71.94999694824219</v>
@@ -4441,11 +4453,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>62.25905609130859</v>
+        <v>62.25905227661133</v>
       </c>
       <c r="C161" t="n">
         <v>76.66999816894531</v>
@@ -4470,11 +4482,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>59.82292938232422</v>
+        <v>59.82294464111328</v>
       </c>
       <c r="C162" t="n">
         <v>73.66999816894531</v>
@@ -4499,11 +4511,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>65.48463439941406</v>
+        <v>65.484619140625</v>
       </c>
       <c r="C163" t="n">
         <v>80.09999847412109</v>
@@ -4528,11 +4540,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>65.90158843994141</v>
+        <v>65.90155792236328</v>
       </c>
       <c r="C164" t="n">
         <v>80.61000061035156</v>
@@ -4557,11 +4569,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>68.36236572265625</v>
+        <v>68.36235046386719</v>
       </c>
       <c r="C165" t="n">
         <v>83.62000274658203</v>
@@ -4586,11 +4598,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>70.10457611083984</v>
+        <v>70.10458374023438</v>
       </c>
       <c r="C166" t="n">
         <v>85.22000122070312</v>
@@ -4615,11 +4627,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>72.19406127929688</v>
+        <v>72.19405364990234</v>
       </c>
       <c r="C167" t="n">
         <v>87.76000213623047</v>
@@ -4644,11 +4656,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>75.31182098388672</v>
+        <v>75.31182861328125</v>
       </c>
       <c r="C168" t="n">
         <v>91.55000305175781</v>
@@ -4673,7 +4685,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4702,11 +4714,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>76.87254333496094</v>
+        <v>76.87253570556641</v>
       </c>
       <c r="C170" t="n">
         <v>92.87999725341797</v>
@@ -4731,11 +4743,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>69.75473022460938</v>
+        <v>69.75471496582031</v>
       </c>
       <c r="C171" t="n">
         <v>84.27999877929688</v>
@@ -4760,7 +4772,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4789,11 +4801,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>74.46707153320312</v>
+        <v>74.46704864501953</v>
       </c>
       <c r="C173" t="n">
         <v>89.23000335693359</v>
@@ -4818,11 +4830,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>76.36147308349609</v>
+        <v>76.36146545410156</v>
       </c>
       <c r="C174" t="n">
         <v>91.5</v>
@@ -4847,11 +4859,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>78.36993408203125</v>
+        <v>78.36991119384766</v>
       </c>
       <c r="C175" t="n">
         <v>93.33000183105469</v>
@@ -4876,11 +4888,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>88.52199554443359</v>
+        <v>88.52196502685547</v>
       </c>
       <c r="C176" t="n">
         <v>105.4199981689453</v>
@@ -4905,11 +4917,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>85.53261566162109</v>
+        <v>85.53260803222656</v>
       </c>
       <c r="C177" t="n">
         <v>101.8600006103516</v>
@@ -4934,11 +4946,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>84.97112274169922</v>
+        <v>84.97111511230469</v>
       </c>
       <c r="C178" t="n">
         <v>100.620002746582</v>
@@ -4963,11 +4975,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>83.77195739746094</v>
+        <v>83.77197265625</v>
       </c>
       <c r="C179" t="n">
         <v>99.19999694824219</v>
@@ -4992,11 +5004,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>84.48977661132812</v>
+        <v>84.48978424072266</v>
       </c>
       <c r="C180" t="n">
         <v>100.0500030517578</v>
@@ -5021,11 +5033,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>84.65215301513672</v>
+        <v>84.65216064453125</v>
       </c>
       <c r="C181" t="n">
         <v>99.66000366210938</v>
@@ -5050,11 +5062,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>87.6590576171875</v>
+        <v>87.65904998779297</v>
       </c>
       <c r="C182" t="n">
         <v>103.1999969482422</v>
@@ -5079,7 +5091,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5108,11 +5120,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>90.59642791748047</v>
+        <v>90.59642028808594</v>
       </c>
       <c r="C184" t="n">
         <v>106</v>
@@ -5137,11 +5149,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>99.59624481201172</v>
+        <v>99.59625244140625</v>
       </c>
       <c r="C185" t="n">
         <v>116.5299987792969</v>
@@ -5166,11 +5178,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>100.7158584594727</v>
+        <v>100.7158508300781</v>
       </c>
       <c r="C186" t="n">
         <v>117.8399963378906</v>
@@ -5195,7 +5207,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5224,11 +5236,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>109.9828567504883</v>
+        <v>109.9828414916992</v>
       </c>
       <c r="C188" t="n">
         <v>128.0399932861328</v>
@@ -5253,11 +5265,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>115.6692657470703</v>
+        <v>115.6692581176758</v>
       </c>
       <c r="C189" t="n">
         <v>134.6600036621094</v>
@@ -5282,7 +5294,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5311,11 +5323,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>125.1079864501953</v>
+        <v>125.1080017089844</v>
       </c>
       <c r="C191" t="n">
         <v>144.9600067138672</v>
@@ -5340,11 +5352,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>130.1050567626953</v>
+        <v>130.1050720214844</v>
       </c>
       <c r="C192" t="n">
         <v>150.75</v>
@@ -5369,11 +5381,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>145.8811187744141</v>
+        <v>145.8811340332031</v>
       </c>
       <c r="C193" t="n">
         <v>168.3600006103516</v>
@@ -5398,11 +5410,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>135.8819274902344</v>
+        <v>135.8819732666016</v>
       </c>
       <c r="C194" t="n">
         <v>156.8200073242188</v>
@@ -5427,11 +5439,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>126.3766098022461</v>
+        <v>126.3765869140625</v>
       </c>
       <c r="C195" t="n">
         <v>145.8500061035156</v>
@@ -5456,7 +5468,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5485,11 +5497,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>139.6020965576172</v>
+        <v>139.6021118164062</v>
       </c>
       <c r="C197" t="n">
         <v>160.2899932861328</v>
@@ -5514,11 +5526,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>111.0267639160156</v>
+        <v>111.026741027832</v>
       </c>
       <c r="C198" t="n">
         <v>127.4800033569336</v>
@@ -5543,11 +5555,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>103.2022323608398</v>
+        <v>103.2022399902344</v>
       </c>
       <c r="C199" t="n">
         <v>117.6500015258789</v>
@@ -5572,11 +5584,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>116.2812347412109</v>
+        <v>116.28125</v>
       </c>
       <c r="C200" t="n">
         <v>132.5599975585938</v>
@@ -5601,7 +5613,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5630,11 +5642,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>89.689697265625</v>
+        <v>89.68967437744141</v>
       </c>
       <c r="C202" t="n">
         <v>101.5999984741211</v>
@@ -5659,11 +5671,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>97.76705169677734</v>
+        <v>97.76704406738281</v>
       </c>
       <c r="C203" t="n">
         <v>110.75</v>
@@ -5688,11 +5700,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>103.9817733764648</v>
+        <v>103.9817810058594</v>
       </c>
       <c r="C204" t="n">
         <v>117.7900009155273</v>
@@ -5717,11 +5729,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>100.1823196411133</v>
+        <v>100.1823120117188</v>
       </c>
       <c r="C205" t="n">
         <v>112.7300033569336</v>
@@ -5746,11 +5758,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>114.8901748657227</v>
+        <v>114.8901824951172</v>
       </c>
       <c r="C206" t="n">
         <v>129.2799987792969</v>
@@ -5775,7 +5787,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5804,11 +5816,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>111.6918869018555</v>
+        <v>111.6918792724609</v>
       </c>
       <c r="C208" t="n">
         <v>124.7699966430664</v>
@@ -5833,11 +5845,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>112.1215591430664</v>
+        <v>112.1215744018555</v>
       </c>
       <c r="C209" t="n">
         <v>125.25</v>
@@ -5862,11 +5874,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>111.4949569702148</v>
+        <v>111.4949340820312</v>
       </c>
       <c r="C210" t="n">
         <v>124.5500030517578</v>
@@ -5891,11 +5903,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>110.5628890991211</v>
+        <v>110.5629043579102</v>
       </c>
       <c r="C211" t="n">
         <v>122.629997253418</v>
@@ -5920,7 +5932,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -5949,7 +5961,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -5978,11 +5990,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>101.8811569213867</v>
+        <v>101.8811492919922</v>
       </c>
       <c r="C214" t="n">
         <v>112.2099990844727</v>
@@ -6007,7 +6019,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6036,7 +6048,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6065,7 +6077,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6094,11 +6106,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>115.7627792358398</v>
+        <v>115.7627868652344</v>
       </c>
       <c r="C218" t="n">
         <v>126.6900024414062</v>
@@ -6123,11 +6135,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>121.7752456665039</v>
+        <v>121.775260925293</v>
       </c>
       <c r="C219" t="n">
         <v>133.2700042724609</v>
@@ -6152,11 +6164,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>119.868408203125</v>
+        <v>119.8684310913086</v>
       </c>
       <c r="C220" t="n">
         <v>130.2200012207031</v>
@@ -6181,7 +6193,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6210,11 +6222,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>101.7068099975586</v>
+        <v>101.7068176269531</v>
       </c>
       <c r="C222" t="n">
         <v>110.4899978637695</v>
@@ -6239,7 +6251,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6268,7 +6280,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6297,7 +6309,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6326,7 +6338,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6355,11 +6367,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>105.6387481689453</v>
+        <v>105.6387405395508</v>
       </c>
       <c r="C227" t="n">
         <v>112.9400024414062</v>
@@ -6384,11 +6396,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>109.2305068969727</v>
+        <v>109.2304916381836</v>
       </c>
       <c r="C228" t="n">
         <v>116.7799987792969</v>
@@ -6413,11 +6425,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>99.72829437255859</v>
+        <v>99.72830200195312</v>
       </c>
       <c r="C229" t="n">
         <v>105.6999969482422</v>
@@ -6442,11 +6454,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>112.5127716064453</v>
+        <v>112.5127639770508</v>
       </c>
       <c r="C230" t="n">
         <v>119.25</v>
@@ -6471,7 +6483,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6500,11 +6512,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>106.4133911132812</v>
+        <v>106.4134063720703</v>
       </c>
       <c r="C232" t="n">
         <v>111.7900009155273</v>
@@ -6529,7 +6541,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6558,7 +6570,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6587,11 +6599,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>101.0193481445312</v>
+        <v>101.0193405151367</v>
       </c>
       <c r="C235" t="n">
         <v>105.120002746582</v>
@@ -6616,11 +6628,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>102.6145782470703</v>
+        <v>102.6145935058594</v>
       </c>
       <c r="C236" t="n">
         <v>106.7799987792969</v>
@@ -6645,11 +6657,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>109.3415145874023</v>
+        <v>109.3415298461914</v>
       </c>
       <c r="C237" t="n">
         <v>113.7799987792969</v>
@@ -6674,7 +6686,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6703,11 +6715,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>120.3127517700195</v>
+        <v>120.312744140625</v>
       </c>
       <c r="C239" t="n">
         <v>124.0899963378906</v>
@@ -6732,11 +6744,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>124.6175994873047</v>
+        <v>124.6175918579102</v>
       </c>
       <c r="C240" t="n">
         <v>128.5299987792969</v>
@@ -6761,7 +6773,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6790,7 +6802,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6819,11 +6831,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>139.3070678710938</v>
+        <v>139.3070831298828</v>
       </c>
       <c r="C243" t="n">
         <v>142.5700073242188</v>
@@ -6848,11 +6860,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>130.1939239501953</v>
+        <v>130.1939086914062</v>
       </c>
       <c r="C244" t="n">
         <v>132.1799926757812</v>
@@ -6877,7 +6889,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6906,11 +6918,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>141.3143005371094</v>
+        <v>141.3142852783203</v>
       </c>
       <c r="C246" t="n">
         <v>143.4700012207031</v>
@@ -6935,7 +6947,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6964,7 +6976,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -6993,7 +7005,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7022,32 +7034,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>133.9600067138672</v>
+        <v>133.8200073242188</v>
       </c>
       <c r="C250" t="n">
-        <v>133.9600067138672</v>
+        <v>133.8200073242188</v>
       </c>
       <c r="D250" t="n">
-        <v>54548700</v>
+        <v>57312600</v>
       </c>
       <c r="E250" t="n">
         <v>4.489999999999999</v>
       </c>
       <c r="F250" t="n">
-        <v>29.8351908048702</v>
+        <v>29.80401053991509</v>
       </c>
       <c r="G250" t="n">
         <v>932338000</v>
       </c>
       <c r="H250" t="n">
-        <v>124896004739.5935</v>
+        <v>124765477988.6475</v>
       </c>
       <c r="I250" t="n">
-        <v>0.05850742970896821</v>
+        <v>0.06147191254673734</v>
       </c>
     </row>
   </sheetData>
@@ -7079,75 +7091,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7183,13 +7195,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40794</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7225,13 +7237,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7267,13 +7279,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7300,7 +7312,7 @@
       <c r="I5" t="n">
         <v>-5.470000000000001</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K5" t="n">
@@ -7313,13 +7325,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7346,7 +7358,7 @@
       <c r="I6" t="n">
         <v>-5.220000000000001</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K6" t="n">
@@ -7359,13 +7371,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40794</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7392,7 +7404,7 @@
       <c r="I7" t="n">
         <v>-5.600000000000001</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K7" t="n">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7438,7 +7450,7 @@
       <c r="I8" t="n">
         <v>-5.41</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K8" t="n">
@@ -7451,13 +7463,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7484,7 +7496,7 @@
       <c r="I9" t="n">
         <v>-0.65</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K9" t="n">
@@ -7497,13 +7509,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7530,7 +7542,7 @@
       <c r="I10" t="n">
         <v>-0.02999999999999997</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="K10" t="n">
@@ -7543,13 +7555,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7576,7 +7588,7 @@
       <c r="I11" t="n">
         <v>0.44</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="K11" t="n">
@@ -7589,13 +7601,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7622,7 +7634,7 @@
       <c r="I12" t="n">
         <v>0.22</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="K12" t="n">
@@ -7635,13 +7647,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7668,7 +7680,7 @@
       <c r="I13" t="n">
         <v>-0.1799999999999999</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K13" t="n">
@@ -7681,13 +7693,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7714,7 +7726,7 @@
       <c r="I14" t="n">
         <v>-0.05000000000000004</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="K14" t="n">
@@ -7727,13 +7739,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7760,7 +7772,7 @@
       <c r="I15" t="n">
         <v>-0.03000000000000004</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="K15" t="n">
@@ -7773,13 +7785,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7806,7 +7818,7 @@
       <c r="I16" t="n">
         <v>0.04999999999999996</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="K16" t="n">
@@ -7819,13 +7831,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7852,7 +7864,7 @@
       <c r="I17" t="n">
         <v>0.6699999999999999</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="K17" t="n">
@@ -7865,13 +7877,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7898,7 +7910,7 @@
       <c r="I18" t="n">
         <v>0.11</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="K18" t="n">
@@ -7911,13 +7923,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7944,7 +7956,7 @@
       <c r="I19" t="n">
         <v>0.24</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="K19" t="n">
@@ -7957,13 +7969,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7990,7 +8002,7 @@
       <c r="I20" t="n">
         <v>0.49</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="K20" t="n">
@@ -8003,13 +8015,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8036,7 +8048,7 @@
       <c r="I21" t="n">
         <v>1.18</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="K21" t="n">
@@ -8049,13 +8061,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8082,7 +8094,7 @@
       <c r="I22" t="n">
         <v>1.82</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="K22" t="n">
@@ -8095,13 +8107,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8128,7 +8140,7 @@
       <c r="I23" t="n">
         <v>1.96</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="K23" t="n">
@@ -8141,13 +8153,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8174,7 +8186,7 @@
       <c r="I24" t="n">
         <v>2.22</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="K24" t="n">
@@ -8187,13 +8199,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8220,7 +8232,7 @@
       <c r="I25" t="n">
         <v>1.64</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="K25" t="n">
@@ -8233,13 +8245,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8266,7 +8278,7 @@
       <c r="I26" t="n">
         <v>1.38</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="K26" t="n">
@@ -8279,13 +8291,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8312,7 +8324,7 @@
       <c r="I27" t="n">
         <v>1.63</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="K27" t="n">
@@ -8325,13 +8337,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8358,7 +8370,7 @@
       <c r="I28" t="n">
         <v>1.66</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K28" t="n">
@@ -8371,13 +8383,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8404,7 +8416,7 @@
       <c r="I29" t="n">
         <v>2.25</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="K29" t="n">
@@ -8417,13 +8429,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42850</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8450,7 +8462,7 @@
       <c r="I30" t="n">
         <v>2.24</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42850</v>
       </c>
       <c r="K30" t="n">
@@ -8463,13 +8475,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8496,7 +8508,7 @@
       <c r="I31" t="n">
         <v>2.22</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="K31" t="n">
@@ -8509,13 +8521,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8542,7 +8554,7 @@
       <c r="I32" t="n">
         <v>3.33</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="K32" t="n">
@@ -8555,13 +8567,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8588,7 +8600,7 @@
       <c r="I33" t="n">
         <v>3.06</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="K33" t="n">
@@ -8601,13 +8613,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8634,7 +8646,7 @@
       <c r="I34" t="n">
         <v>3.36</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="K34" t="n">
@@ -8647,13 +8659,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43304</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8680,7 +8692,7 @@
       <c r="I35" t="n">
         <v>3.48</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43304</v>
       </c>
       <c r="K35" t="n">
@@ -8693,13 +8705,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43395</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8726,7 +8738,7 @@
       <c r="I36" t="n">
         <v>2.45</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43395</v>
       </c>
       <c r="K36" t="n">
@@ -8739,13 +8751,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8772,7 +8784,7 @@
       <c r="I37" t="n">
         <v>2.84</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="K37" t="n">
@@ -8785,13 +8797,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8818,7 +8830,7 @@
       <c r="I38" t="n">
         <v>2.71</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="K38" t="n">
@@ -8831,13 +8843,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43668</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8864,7 +8876,7 @@
       <c r="I39" t="n">
         <v>2.69</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43668</v>
       </c>
       <c r="K39" t="n">
@@ -8877,13 +8889,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43759</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8910,7 +8922,7 @@
       <c r="I40" t="n">
         <v>2.8</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43759</v>
       </c>
       <c r="K40" t="n">
@@ -8923,13 +8935,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43872</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8956,7 +8968,7 @@
       <c r="I41" t="n">
         <v>2.47</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43872</v>
       </c>
       <c r="K41" t="n">
@@ -8969,13 +8981,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9002,7 +9014,7 @@
       <c r="I42" t="n">
         <v>2.62</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K42" t="n">
@@ -9015,13 +9027,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9048,7 +9060,7 @@
       <c r="I43" t="n">
         <v>2.56</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="K43" t="n">
@@ -9061,13 +9073,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9094,7 +9106,7 @@
       <c r="I44" t="n">
         <v>2.25</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="K44" t="n">
@@ -9107,13 +9119,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9140,7 +9152,7 @@
       <c r="I45" t="n">
         <v>2.02</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="K45" t="n">
@@ -9153,13 +9165,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9186,7 +9198,7 @@
       <c r="I46" t="n">
         <v>1.81</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="K46" t="n">
@@ -9199,13 +9211,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9232,7 +9244,7 @@
       <c r="I47" t="n">
         <v>2.08</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="K47" t="n">
@@ -9245,13 +9257,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9278,7 +9290,7 @@
       <c r="I48" t="n">
         <v>2.65</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="K48" t="n">
@@ -9291,13 +9303,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9324,7 +9336,7 @@
       <c r="I49" t="n">
         <v>3.94</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="K49" t="n">
@@ -9337,13 +9349,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9370,7 +9382,7 @@
       <c r="I50" t="n">
         <v>4.99</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="K50" t="n">
@@ -9383,13 +9395,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44781</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9416,7 +9428,7 @@
       <c r="I51" t="n">
         <v>5</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44781</v>
       </c>
       <c r="K51" t="n">
@@ -9429,13 +9441,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9462,7 +9474,7 @@
       <c r="I52" t="n">
         <v>5.39</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="K52" t="n">
@@ -9475,13 +9487,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9508,7 +9520,7 @@
       <c r="I53" t="n">
         <v>4.350000000000001</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="K53" t="n">
@@ -9521,13 +9533,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9554,7 +9566,7 @@
       <c r="I54" t="n">
         <v>3.31</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="K54" t="n">
@@ -9567,13 +9579,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9600,7 +9612,7 @@
       <c r="I55" t="n">
         <v>3.8</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="K55" t="n">
@@ -9613,13 +9625,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9646,7 +9658,7 @@
       <c r="I56" t="n">
         <v>3.24</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="K56" t="n">
@@ -9659,13 +9671,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9692,7 +9704,7 @@
       <c r="I57" t="n">
         <v>3.29</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="K57" t="n">
@@ -9705,13 +9717,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9738,7 +9750,7 @@
       <c r="I58" t="n">
         <v>3.42</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="K58" t="n">
@@ -9751,13 +9763,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9784,7 +9796,7 @@
       <c r="I59" t="n">
         <v>3.03</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="K59" t="n">
@@ -9797,13 +9809,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9830,7 +9842,7 @@
       <c r="I60" t="n">
         <v>3.31</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="K60" t="n">
@@ -9843,13 +9855,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9876,7 +9888,7 @@
       <c r="I61" t="n">
         <v>4</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="K61" t="n">
@@ -9889,13 +9901,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9922,7 +9934,7 @@
       <c r="I62" t="n">
         <v>4.000000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="K62" t="n">
@@ -9935,13 +9947,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9968,7 +9980,7 @@
       <c r="I63" t="n">
         <v>3.69</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="K63" t="n">
@@ -9981,13 +9993,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10014,7 +10026,7 @@
       <c r="I64" t="n">
         <v>3.43</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="K64" t="n">
@@ -10027,13 +10039,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10060,7 +10072,7 @@
       <c r="I65" t="n">
         <v>3.55</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="K65" t="n">
@@ -10073,13 +10085,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10106,7 +10118,7 @@
       <c r="I66" t="n">
         <v>3.97</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K66" t="n">
@@ -10119,13 +10131,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10146,7 +10158,7 @@
       <c r="I67" t="n">
         <v>4.489999999999999</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K67" t="n">
@@ -10183,52 +10195,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40392</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40393</v>
       </c>
       <c r="C2" t="n">
@@ -10257,10 +10269,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40484</v>
       </c>
       <c r="C3" t="n">
@@ -10289,10 +10301,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40590</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="C4" t="n">
@@ -10321,10 +10333,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40668</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="C5" t="n">
@@ -10353,10 +10365,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40757</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40794</v>
       </c>
       <c r="C6" t="n">
@@ -10385,10 +10397,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40846</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="C7" t="n">
@@ -10417,10 +10429,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40961</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="C8" t="n">
@@ -10449,10 +10461,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41030</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="C9" t="n">
@@ -10481,10 +10493,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41122</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="C10" t="n">
@@ -10513,10 +10525,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41214</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="C11" t="n">
@@ -10545,10 +10557,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41327</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C12" t="n">
@@ -10577,10 +10589,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41395</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="C13" t="n">
@@ -10609,10 +10621,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41487</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C14" t="n">
@@ -10641,10 +10653,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41577</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="C15" t="n">
@@ -10673,10 +10685,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41691</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="C16" t="n">
@@ -10705,10 +10717,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41760</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="C17" t="n">
@@ -10737,10 +10749,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41852</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="C18" t="n">
@@ -10769,10 +10781,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="C19" t="n">
@@ -10801,10 +10813,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42055</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="C20" t="n">
@@ -10833,10 +10845,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42121</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="C21" t="n">
@@ -10865,10 +10877,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42212</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="C22" t="n">
@@ -10897,10 +10909,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42304</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="C23" t="n">
@@ -10929,10 +10941,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42412</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="C24" t="n">
@@ -10961,10 +10973,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42492</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="C25" t="n">
@@ -10993,10 +11005,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42573</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="C26" t="n">
@@ -11025,10 +11037,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42671</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C27" t="n">
@@ -11057,10 +11069,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42776</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="C28" t="n">
@@ -11089,10 +11101,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42850</v>
       </c>
       <c r="C29" t="n">
@@ -11121,10 +11133,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42940</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="C30" t="n">
@@ -11153,10 +11165,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43033</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C31" t="n">
@@ -11185,10 +11197,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43143</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="C32" t="n">
@@ -11217,10 +11229,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43209</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="C33" t="n">
@@ -11249,10 +11261,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43300</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43304</v>
       </c>
       <c r="C34" t="n">
@@ -11281,10 +11293,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43391</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43395</v>
       </c>
       <c r="C35" t="n">
@@ -11313,10 +11325,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43507</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="C36" t="n">
@@ -11345,10 +11357,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43573</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="C37" t="n">
@@ -11377,10 +11389,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43663</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43668</v>
       </c>
       <c r="C38" t="n">
@@ -11409,10 +11421,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43756</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43759</v>
       </c>
       <c r="C39" t="n">
@@ -11441,10 +11453,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43865</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43872</v>
       </c>
       <c r="C40" t="n">
@@ -11473,10 +11485,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43948</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C41" t="n">
@@ -11505,10 +11517,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44036</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="C42" t="n">
@@ -11537,10 +11549,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44127</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="C43" t="n">
@@ -11569,10 +11581,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44232</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="C44" t="n">
@@ -11601,10 +11613,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44309</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="C45" t="n">
@@ -11633,10 +11645,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44400</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="C46" t="n">
@@ -11665,10 +11677,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44491</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="C47" t="n">
@@ -11697,10 +11709,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44599</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="C48" t="n">
@@ -11729,10 +11741,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44673</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="C49" t="n">
@@ -11761,10 +11773,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44777</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44781</v>
       </c>
       <c r="C50" t="n">
@@ -11793,10 +11805,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44858</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="C51" t="n">
@@ -11825,10 +11837,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44970</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="C52" t="n">
@@ -11857,10 +11869,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45042</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="C53" t="n">
@@ -11889,10 +11901,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="C54" t="n">
@@ -11921,10 +11933,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45224</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="C55" t="n">
@@ -11953,10 +11965,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45331</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="C56" t="n">
@@ -11985,10 +11997,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45404</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="C57" t="n">
@@ -12017,10 +12029,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45497</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="C58" t="n">
@@ -12049,10 +12061,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45588</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="C59" t="n">
@@ -12081,10 +12093,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45700</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="C60" t="n">
@@ -12113,10 +12125,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45772</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="C61" t="n">
@@ -12145,10 +12157,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45863</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="C62" t="n">
@@ -12177,10 +12189,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45954</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="C63" t="n">
@@ -12209,10 +12221,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46064</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="C64" t="n">
@@ -12241,10 +12253,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46140</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C65" t="n">
@@ -12291,12 +12303,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/PLD.xlsx
+++ b/salidas/empresas/PLD.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>26.47859001159668</v>
+        <v>26.47858047485352</v>
       </c>
       <c r="C2" t="n">
         <v>52.20000076293945</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>27.21410751342773</v>
+        <v>27.21410369873047</v>
       </c>
       <c r="C3" t="n">
         <v>53.65000152587891</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>27.52859878540039</v>
+        <v>27.52860069274902</v>
       </c>
       <c r="C4" t="n">
         <v>54.27000045776367</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>25.58008003234863</v>
+        <v>25.58006858825684</v>
       </c>
       <c r="C5" t="n">
         <v>49.9900016784668</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>25.29351806640625</v>
+        <v>25.29351425170898</v>
       </c>
       <c r="C6" t="n">
         <v>49.43000030517578</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>25.86663055419922</v>
+        <v>25.86663246154785</v>
       </c>
       <c r="C7" t="n">
         <v>50.54999923706055</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>27.07032775878906</v>
+        <v>27.0703296661377</v>
       </c>
       <c r="C8" t="n">
         <v>52.43000030517578</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>28.82579040527344</v>
+        <v>28.82579231262207</v>
       </c>
       <c r="C9" t="n">
         <v>55.83000183105469</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>28.45404052734375</v>
+        <v>28.45404624938965</v>
       </c>
       <c r="C10" t="n">
         <v>55.11000061035156</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>30.4057788848877</v>
+        <v>30.40579986572266</v>
       </c>
       <c r="C11" t="n">
         <v>58.40999984741211</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>31.89458656311035</v>
+        <v>31.89458847045898</v>
       </c>
       <c r="C12" t="n">
         <v>61.27000045776367</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>30.74802589416504</v>
+        <v>30.74801063537598</v>
       </c>
       <c r="C13" t="n">
         <v>58.61000061035156</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>31.92317581176758</v>
+        <v>31.92316246032715</v>
       </c>
       <c r="C14" t="n">
         <v>60.84999847412109</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>30.84770011901855</v>
+        <v>30.84769630432129</v>
       </c>
       <c r="C15" t="n">
         <v>58.79999923706055</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>30.84245491027832</v>
+        <v>30.84245109558105</v>
       </c>
       <c r="C16" t="n">
         <v>58.79000091552734</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>32.2255973815918</v>
+        <v>32.22557830810547</v>
       </c>
       <c r="C17" t="n">
         <v>60.90999984741211</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>30.60662841796875</v>
+        <v>30.60663223266602</v>
       </c>
       <c r="C18" t="n">
         <v>57.84999847412109</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>28.15703392028809</v>
+        <v>28.15705108642578</v>
       </c>
       <c r="C19" t="n">
         <v>53.22000122070312</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>29.35121726989746</v>
+        <v>29.35120964050293</v>
       </c>
       <c r="C21" t="n">
         <v>54.97999954223633</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>31.9297046661377</v>
+        <v>31.92971038818359</v>
       </c>
       <c r="C22" t="n">
         <v>59.81000137329102</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>35.16736221313477</v>
+        <v>35.16739273071289</v>
       </c>
       <c r="C23" t="n">
         <v>65.34999847412109</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>32.91257858276367</v>
+        <v>32.91259384155273</v>
       </c>
       <c r="C24" t="n">
         <v>61.15999984741211</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>31.25691986083984</v>
+        <v>31.25692749023438</v>
       </c>
       <c r="C25" t="n">
         <v>57.56000137329102</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>27.46112632751465</v>
+        <v>27.46113777160645</v>
       </c>
       <c r="C26" t="n">
         <v>50.56999969482422</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>27.24935340881348</v>
+        <v>27.24935913085938</v>
       </c>
       <c r="C27" t="n">
         <v>50.18000030517578</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>29.55180740356445</v>
+        <v>29.55179977416992</v>
       </c>
       <c r="C28" t="n">
         <v>54.41999816894531</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>31.64771270751953</v>
+        <v>31.6476993560791</v>
       </c>
       <c r="C29" t="n">
         <v>57.75</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>32.29985046386719</v>
+        <v>32.29984664916992</v>
       </c>
       <c r="C30" t="n">
         <v>58.93999862670898</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>27.60885810852051</v>
+        <v>27.60886383056641</v>
       </c>
       <c r="C31" t="n">
         <v>50.38000106811523</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>27.11051177978516</v>
+        <v>27.11051750183105</v>
       </c>
       <c r="C32" t="n">
         <v>48.95999908447266</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>25.13369369506836</v>
+        <v>25.13370132446289</v>
       </c>
       <c r="C33" t="n">
         <v>45.38999938964844</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>25.08386039733887</v>
+        <v>25.08387565612793</v>
       </c>
       <c r="C34" t="n">
         <v>45.29999923706055</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>13.46736431121826</v>
+        <v>13.46735954284668</v>
       </c>
       <c r="C35" t="n">
         <v>24.03000068664551</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>9.650769233703613</v>
+        <v>9.650765419006348</v>
       </c>
       <c r="C36" t="n">
         <v>17.21999931335449</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>13.12549686431885</v>
+        <v>13.12549209594727</v>
       </c>
       <c r="C37" t="n">
         <v>23.42000007629395</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>8.070331573486328</v>
+        <v>8.070328712463379</v>
       </c>
       <c r="C40" t="n">
         <v>14.39999961853027</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>10.90725708007812</v>
+        <v>10.90725612640381</v>
       </c>
       <c r="C41" t="n">
         <v>19.09000015258789</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>10.19876766204834</v>
+        <v>10.19877052307129</v>
       </c>
       <c r="C42" t="n">
         <v>17.85000038146973</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.74727725982666</v>
+        <v>10.74727821350098</v>
       </c>
       <c r="C43" t="n">
         <v>18.80999946594238</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>11.48966789245605</v>
+        <v>11.48966979980469</v>
       </c>
       <c r="C44" t="n">
         <v>19.80999946594238</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>13.24124813079834</v>
+        <v>13.24125003814697</v>
       </c>
       <c r="C45" t="n">
         <v>22.82999992370605</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>13.31085014343262</v>
+        <v>13.31084156036377</v>
       </c>
       <c r="C46" t="n">
         <v>22.95000076293945</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>12.90570640563965</v>
+        <v>12.9057092666626</v>
       </c>
       <c r="C47" t="n">
         <v>21.97999954223633</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>13.82754516601562</v>
+        <v>13.82754325866699</v>
       </c>
       <c r="C48" t="n">
         <v>23.54999923706055</v>
@@ -1391,7 +1391,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>15.16920757293701</v>
+        <v>15.16920852661133</v>
       </c>
       <c r="C49" t="n">
         <v>25.54999923706055</v>
@@ -1410,7 +1410,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>14.24896717071533</v>
+        <v>14.24896144866943</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1429,7 +1429,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>14.45082473754883</v>
+        <v>14.45081901550293</v>
       </c>
       <c r="C51" t="n">
         <v>24.34000015258789</v>
@@ -1448,7 +1448,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>16.33729934692383</v>
+        <v>16.33730125427246</v>
       </c>
       <c r="C52" t="n">
         <v>27.23999977111816</v>
@@ -1467,7 +1467,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>16.70914459228516</v>
+        <v>16.70914840698242</v>
       </c>
       <c r="C53" t="n">
         <v>27.86000061035156</v>
@@ -1486,7 +1486,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>15.55162239074707</v>
+        <v>15.55162143707275</v>
       </c>
       <c r="C54" t="n">
         <v>25.93000030517578</v>
@@ -1505,7 +1505,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>14.22017192840576</v>
+        <v>14.2201681137085</v>
       </c>
       <c r="C55" t="n">
         <v>23.70999908447266</v>
@@ -1524,7 +1524,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>15.14875411987305</v>
+        <v>15.14876174926758</v>
       </c>
       <c r="C56" t="n">
         <v>24.95999908447266</v>
@@ -1543,7 +1543,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>14.4386625289917</v>
+        <v>14.43866539001465</v>
       </c>
       <c r="C57" t="n">
         <v>23.79000091552734</v>
@@ -1568,7 +1568,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>16.06521034240723</v>
+        <v>16.06520462036133</v>
       </c>
       <c r="C58" t="n">
         <v>26.46999931335449</v>
@@ -1593,7 +1593,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>17.29203033447266</v>
+        <v>17.29203224182129</v>
       </c>
       <c r="C59" t="n">
         <v>28.19000053405762</v>
@@ -1618,7 +1618,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>17.90543365478516</v>
+        <v>17.90543556213379</v>
       </c>
       <c r="C60" t="n">
         <v>29.19000053405762</v>
@@ -1643,7 +1643,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>19.6265811920166</v>
+        <v>19.62658500671387</v>
       </c>
       <c r="C61" t="n">
         <v>31.70999908447266</v>
@@ -1668,7 +1668,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>20.76542663574219</v>
+        <v>20.76543235778809</v>
       </c>
       <c r="C62" t="n">
         <v>33.54999923706055</v>
@@ -1693,7 +1693,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>22.70574569702148</v>
+        <v>22.70574378967285</v>
       </c>
       <c r="C63" t="n">
         <v>36.38000106811523</v>
@@ -1718,7 +1718,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>22.44985198974609</v>
+        <v>22.44985961914062</v>
       </c>
       <c r="C64" t="n">
         <v>35.97000122070312</v>
@@ -1743,7 +1743,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>22.71821975708008</v>
+        <v>22.71822357177734</v>
       </c>
       <c r="C65" t="n">
         <v>36.40000152587891</v>
@@ -1768,7 +1768,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>23.26938056945801</v>
+        <v>23.26937675476074</v>
       </c>
       <c r="C66" t="n">
         <v>36.9900016784668</v>
@@ -1793,7 +1793,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>22.54594039916992</v>
+        <v>22.54594421386719</v>
       </c>
       <c r="C67" t="n">
         <v>35.84000015258789</v>
@@ -1818,7 +1818,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>22.41383361816406</v>
+        <v>22.4138355255127</v>
       </c>
       <c r="C68" t="n">
         <v>35.63000106811523</v>
@@ -1843,7 +1843,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>17.1296272277832</v>
+        <v>17.12963485717773</v>
       </c>
       <c r="C69" t="n">
         <v>27.22999954223633</v>
@@ -1868,7 +1868,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>15.41752529144287</v>
+        <v>15.41752910614014</v>
       </c>
       <c r="C70" t="n">
         <v>24.25</v>
@@ -1893,7 +1893,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>18.92065238952637</v>
+        <v>18.92064666748047</v>
       </c>
       <c r="C71" t="n">
         <v>29.76000022888184</v>
@@ -1918,7 +1918,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>17.6872444152832</v>
+        <v>17.68724632263184</v>
       </c>
       <c r="C72" t="n">
         <v>27.81999969482422</v>
@@ -1943,7 +1943,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>18.36747741699219</v>
+        <v>18.36748313903809</v>
       </c>
       <c r="C73" t="n">
         <v>28.59000015258789</v>
@@ -1968,7 +1968,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>20.37190628051758</v>
+        <v>20.37191009521484</v>
       </c>
       <c r="C74" t="n">
         <v>31.70999908447266</v>
@@ -1993,7 +1993,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>21.62467384338379</v>
+        <v>21.62466812133789</v>
       </c>
       <c r="C75" t="n">
         <v>33.65999984741211</v>
@@ -2020,7 +2020,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>23.33181190490723</v>
+        <v>23.33180618286133</v>
       </c>
       <c r="C76" t="n">
         <v>36.02000045776367</v>
@@ -2047,7 +2047,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>23.16338920593262</v>
+        <v>23.16339302062988</v>
       </c>
       <c r="C77" t="n">
         <v>35.7599983215332</v>
@@ -2074,7 +2074,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>20.71491432189941</v>
+        <v>20.71491241455078</v>
       </c>
       <c r="C78" t="n">
         <v>31.97999954223633</v>
@@ -2101,7 +2101,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>21.7145938873291</v>
+        <v>21.71459197998047</v>
       </c>
       <c r="C79" t="n">
         <v>33.22999954223633</v>
@@ -2155,7 +2155,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>22.32884979248047</v>
+        <v>22.32884788513184</v>
       </c>
       <c r="C81" t="n">
         <v>34.16999816894531</v>
@@ -2184,7 +2184,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>23.06936454772949</v>
+        <v>23.06937026977539</v>
       </c>
       <c r="C82" t="n">
         <v>35.02999877929688</v>
@@ -2213,7 +2213,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>22.58203125</v>
+        <v>22.58203315734863</v>
       </c>
       <c r="C83" t="n">
         <v>34.29000091552734</v>
@@ -2242,7 +2242,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>22.35153007507324</v>
+        <v>22.35154342651367</v>
       </c>
       <c r="C84" t="n">
         <v>33.93999862670898</v>
@@ -2271,7 +2271,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>24.22316741943359</v>
+        <v>24.22316932678223</v>
       </c>
       <c r="C85" t="n">
         <v>36.4900016784668</v>
@@ -2300,7 +2300,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>26.48682975769043</v>
+        <v>26.48683738708496</v>
       </c>
       <c r="C86" t="n">
         <v>39.90000152587891</v>
@@ -2329,7 +2329,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>25.84955215454102</v>
+        <v>25.84955024719238</v>
       </c>
       <c r="C87" t="n">
         <v>38.93999862670898</v>
@@ -2356,7 +2356,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>26.72965812683105</v>
+        <v>26.72965240478516</v>
       </c>
       <c r="C88" t="n">
         <v>39.97999954223633</v>
@@ -2383,7 +2383,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>28.04675102233887</v>
+        <v>28.0467472076416</v>
       </c>
       <c r="C89" t="n">
         <v>41.95000076293945</v>
@@ -2491,7 +2491,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>23.72985076904297</v>
+        <v>23.7298412322998</v>
       </c>
       <c r="C93" t="n">
         <v>35.2400016784668</v>
@@ -2545,7 +2545,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>27.10421371459961</v>
+        <v>27.10420799255371</v>
       </c>
       <c r="C95" t="n">
         <v>39.95000076293945</v>
@@ -2572,7 +2572,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>25.73373794555664</v>
+        <v>25.73373413085938</v>
       </c>
       <c r="C96" t="n">
         <v>37.93000030517578</v>
@@ -2601,7 +2601,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>25.2637825012207</v>
+        <v>25.26377296447754</v>
       </c>
       <c r="C97" t="n">
         <v>36.95000076293945</v>
@@ -2630,7 +2630,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>26.5013256072998</v>
+        <v>26.50132369995117</v>
       </c>
       <c r="C98" t="n">
         <v>38.7599983215332</v>
@@ -2659,7 +2659,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>28.16277885437012</v>
+        <v>28.16278266906738</v>
       </c>
       <c r="C99" t="n">
         <v>41.18999862670898</v>
@@ -2688,7 +2688,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>28.14388275146484</v>
+        <v>28.14388465881348</v>
       </c>
       <c r="C100" t="n">
         <v>40.83000183105469</v>
@@ -2717,7 +2717,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>28.00603675842285</v>
+        <v>28.00603103637695</v>
       </c>
       <c r="C101" t="n">
         <v>40.63000106811523</v>
@@ -2746,7 +2746,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>28.61260223388672</v>
+        <v>28.61260604858398</v>
       </c>
       <c r="C102" t="n">
         <v>41.5099983215332</v>
@@ -2775,7 +2775,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>28.54639434814453</v>
+        <v>28.54638481140137</v>
       </c>
       <c r="C103" t="n">
         <v>41.09000015258789</v>
@@ -2833,7 +2833,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>28.44217491149902</v>
+        <v>28.44217109680176</v>
       </c>
       <c r="C105" t="n">
         <v>40.93999862670898</v>
@@ -2862,7 +2862,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>26.41481971740723</v>
+        <v>26.41482925415039</v>
       </c>
       <c r="C106" t="n">
         <v>37.70000076293945</v>
@@ -2891,7 +2891,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>29.18243217468262</v>
+        <v>29.18243026733398</v>
       </c>
       <c r="C107" t="n">
         <v>41.65000152587891</v>
@@ -2920,7 +2920,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>29.62383460998535</v>
+        <v>29.62384796142578</v>
       </c>
       <c r="C108" t="n">
         <v>42.27999877929688</v>
@@ -2949,7 +2949,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>30.3867359161377</v>
+        <v>30.38673782348633</v>
       </c>
       <c r="C109" t="n">
         <v>43.02999877929688</v>
@@ -3007,7 +3007,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>30.1607551574707</v>
+        <v>30.16076278686523</v>
       </c>
       <c r="C111" t="n">
         <v>42.70999908447266</v>
@@ -3036,7 +3036,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>31.02410125732422</v>
+        <v>31.02410888671875</v>
       </c>
       <c r="C112" t="n">
         <v>43.56000137329102</v>
@@ -3065,7 +3065,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>28.63106346130371</v>
+        <v>28.63106155395508</v>
       </c>
       <c r="C113" t="n">
         <v>40.20000076293945</v>
@@ -3094,7 +3094,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>28.19661331176758</v>
+        <v>28.19660186767578</v>
       </c>
       <c r="C114" t="n">
         <v>39.59000015258789</v>
@@ -3152,7 +3152,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>29.18708229064941</v>
+        <v>29.18707847595215</v>
       </c>
       <c r="C116" t="n">
         <v>40.61000061035156</v>
@@ -3181,7 +3181,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>27.31122970581055</v>
+        <v>27.31122589111328</v>
       </c>
       <c r="C117" t="n">
         <v>38</v>
@@ -3210,7 +3210,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>28.25756645202637</v>
+        <v>28.257568359375</v>
       </c>
       <c r="C118" t="n">
         <v>38.90000152587891</v>
@@ -3239,7 +3239,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>31.03973770141602</v>
+        <v>31.03973960876465</v>
       </c>
       <c r="C119" t="n">
         <v>42.72999954223633</v>
@@ -3268,7 +3268,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>31.05426979064941</v>
+        <v>31.05426025390625</v>
       </c>
       <c r="C120" t="n">
         <v>42.75</v>
@@ -3297,7 +3297,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>31.47760772705078</v>
+        <v>31.47761344909668</v>
       </c>
       <c r="C121" t="n">
         <v>42.91999816894531</v>
@@ -3326,7 +3326,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>28.9473762512207</v>
+        <v>28.94738960266113</v>
       </c>
       <c r="C122" t="n">
         <v>39.47000122070312</v>
@@ -3355,7 +3355,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>28.20663833618164</v>
+        <v>28.2066535949707</v>
       </c>
       <c r="C123" t="n">
         <v>38.45999908447266</v>
@@ -3384,7 +3384,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>32.72626495361328</v>
+        <v>32.72625350952148</v>
       </c>
       <c r="C124" t="n">
         <v>44.18000030517578</v>
@@ -3413,7 +3413,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>33.63737487792969</v>
+        <v>33.63738250732422</v>
       </c>
       <c r="C125" t="n">
         <v>45.40999984741211</v>
@@ -3442,7 +3442,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>35.20777893066406</v>
+        <v>35.20776748657227</v>
       </c>
       <c r="C126" t="n">
         <v>47.52999877929688</v>
@@ -3471,7 +3471,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>36.63804626464844</v>
+        <v>36.63805389404297</v>
       </c>
       <c r="C127" t="n">
         <v>49.04000091552734</v>
@@ -3500,7 +3500,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>40.70977783203125</v>
+        <v>40.70977401733398</v>
       </c>
       <c r="C128" t="n">
         <v>54.4900016784668</v>
@@ -3529,7 +3529,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>39.67876434326172</v>
+        <v>39.67877578735352</v>
       </c>
       <c r="C129" t="n">
         <v>53.11000061035156</v>
@@ -3587,7 +3587,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>39.2894287109375</v>
+        <v>39.2894401550293</v>
       </c>
       <c r="C131" t="n">
         <v>52.15999984741211</v>
@@ -3616,7 +3616,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>38.3403434753418</v>
+        <v>38.34035491943359</v>
       </c>
       <c r="C132" t="n">
         <v>50.90000152587891</v>
@@ -3645,7 +3645,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>40.08929443359375</v>
+        <v>40.08927154541016</v>
       </c>
       <c r="C133" t="n">
         <v>52.79000091552734</v>
@@ -3674,7 +3674,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>37.09720993041992</v>
+        <v>37.09719848632812</v>
       </c>
       <c r="C134" t="n">
         <v>48.84999847412109</v>
@@ -3703,7 +3703,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>38.76790618896484</v>
+        <v>38.76789474487305</v>
       </c>
       <c r="C135" t="n">
         <v>51.04999923706055</v>
@@ -3732,7 +3732,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>39.75229644775391</v>
+        <v>39.75229263305664</v>
       </c>
       <c r="C136" t="n">
         <v>51.88000106811523</v>
@@ -3819,7 +3819,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>45.2807731628418</v>
+        <v>45.28078079223633</v>
       </c>
       <c r="C139" t="n">
         <v>58.63999938964844</v>
@@ -3848,7 +3848,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>46.9564208984375</v>
+        <v>46.95641708374023</v>
       </c>
       <c r="C140" t="n">
         <v>60.81000137329102</v>
@@ -3877,7 +3877,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>48.92548370361328</v>
+        <v>48.92547607421875</v>
       </c>
       <c r="C141" t="n">
         <v>63.36000061035156</v>
@@ -3906,7 +3906,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>49.33518218994141</v>
+        <v>49.33517456054688</v>
       </c>
       <c r="C142" t="n">
         <v>63.45999908447266</v>
@@ -3935,7 +3935,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>50.20589065551758</v>
+        <v>50.20588684082031</v>
       </c>
       <c r="C143" t="n">
         <v>64.58000183105469</v>
@@ -3964,7 +3964,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>51.48863220214844</v>
+        <v>51.4886360168457</v>
       </c>
       <c r="C144" t="n">
         <v>66.23000335693359</v>
@@ -3993,7 +3993,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>50.4885139465332</v>
+        <v>50.48851776123047</v>
       </c>
       <c r="C145" t="n">
         <v>64.51000213623047</v>
@@ -4022,7 +4022,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>50.95810699462891</v>
+        <v>50.95811462402344</v>
       </c>
       <c r="C146" t="n">
         <v>65.11000061035156</v>
@@ -4051,7 +4051,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>47.49098205566406</v>
+        <v>47.49098968505859</v>
       </c>
       <c r="C147" t="n">
         <v>60.68000030517578</v>
@@ -4080,7 +4080,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>49.67517471313477</v>
+        <v>49.6751594543457</v>
       </c>
       <c r="C148" t="n">
         <v>62.9900016784668</v>
@@ -4109,7 +4109,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>51.1893196105957</v>
+        <v>51.1893310546875</v>
       </c>
       <c r="C149" t="n">
         <v>64.91000366210938</v>
@@ -4167,7 +4167,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>52.18681335449219</v>
+        <v>52.18682861328125</v>
       </c>
       <c r="C151" t="n">
         <v>65.69000244140625</v>
@@ -4196,7 +4196,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>52.13120269775391</v>
+        <v>52.1312141418457</v>
       </c>
       <c r="C152" t="n">
         <v>65.62000274658203</v>
@@ -4225,7 +4225,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>53.37053680419922</v>
+        <v>53.37054443359375</v>
       </c>
       <c r="C153" t="n">
         <v>67.18000030517578</v>
@@ -4283,7 +4283,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>51.58393478393555</v>
+        <v>51.58393859863281</v>
       </c>
       <c r="C155" t="n">
         <v>64.47000122070312</v>
@@ -4312,7 +4312,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>53.88027572631836</v>
+        <v>53.88028717041016</v>
       </c>
       <c r="C156" t="n">
         <v>67.33999633789062</v>
@@ -4341,7 +4341,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>47.33378982543945</v>
+        <v>47.33379364013672</v>
       </c>
       <c r="C157" t="n">
         <v>58.72000122070312</v>
@@ -4370,7 +4370,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>55.74941253662109</v>
+        <v>55.74941635131836</v>
       </c>
       <c r="C158" t="n">
         <v>69.16000366210938</v>
@@ -4399,7 +4399,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>56.47489166259766</v>
+        <v>56.47488021850586</v>
       </c>
       <c r="C159" t="n">
         <v>70.05999755859375</v>
@@ -4428,7 +4428,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>58.42621612548828</v>
+        <v>58.42622756958008</v>
       </c>
       <c r="C160" t="n">
         <v>71.94999694824219</v>
@@ -4457,7 +4457,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>62.25905227661133</v>
+        <v>62.25904846191406</v>
       </c>
       <c r="C161" t="n">
         <v>76.66999816894531</v>
@@ -4486,7 +4486,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>59.82294464111328</v>
+        <v>59.82292938232422</v>
       </c>
       <c r="C162" t="n">
         <v>73.66999816894531</v>
@@ -4544,7 +4544,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>65.90155792236328</v>
+        <v>65.90158081054688</v>
       </c>
       <c r="C164" t="n">
         <v>80.61000061035156</v>
@@ -4573,7 +4573,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>68.36235046386719</v>
+        <v>68.36233520507812</v>
       </c>
       <c r="C165" t="n">
         <v>83.62000274658203</v>
@@ -4602,7 +4602,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>70.10458374023438</v>
+        <v>70.10457611083984</v>
       </c>
       <c r="C166" t="n">
         <v>85.22000122070312</v>
@@ -4631,7 +4631,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>72.19405364990234</v>
+        <v>72.19403839111328</v>
       </c>
       <c r="C167" t="n">
         <v>87.76000213623047</v>
@@ -4660,7 +4660,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>75.31182861328125</v>
+        <v>75.31181335449219</v>
       </c>
       <c r="C168" t="n">
         <v>91.55000305175781</v>
@@ -4718,7 +4718,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>76.87253570556641</v>
+        <v>76.87255096435547</v>
       </c>
       <c r="C170" t="n">
         <v>92.87999725341797</v>
@@ -4747,7 +4747,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>69.75471496582031</v>
+        <v>69.75474548339844</v>
       </c>
       <c r="C171" t="n">
         <v>84.27999877929688</v>
@@ -4776,7 +4776,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>67.07292938232422</v>
+        <v>67.07291412353516</v>
       </c>
       <c r="C172" t="n">
         <v>80.37000274658203</v>
@@ -4805,7 +4805,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>74.46704864501953</v>
+        <v>74.46705627441406</v>
       </c>
       <c r="C173" t="n">
         <v>89.23000335693359</v>
@@ -4834,7 +4834,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>76.36146545410156</v>
+        <v>76.36147308349609</v>
       </c>
       <c r="C174" t="n">
         <v>91.5</v>
@@ -4863,7 +4863,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>78.36991119384766</v>
+        <v>78.36994171142578</v>
       </c>
       <c r="C175" t="n">
         <v>93.33000183105469</v>
@@ -4892,7 +4892,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>88.52196502685547</v>
+        <v>88.52198791503906</v>
       </c>
       <c r="C176" t="n">
         <v>105.4199981689453</v>
@@ -4921,7 +4921,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>85.53260803222656</v>
+        <v>85.53262329101562</v>
       </c>
       <c r="C177" t="n">
         <v>101.8600006103516</v>
@@ -4950,7 +4950,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>84.97111511230469</v>
+        <v>84.97109222412109</v>
       </c>
       <c r="C178" t="n">
         <v>100.620002746582</v>
@@ -5037,7 +5037,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>84.65216064453125</v>
+        <v>84.65215301513672</v>
       </c>
       <c r="C181" t="n">
         <v>99.66000366210938</v>
@@ -5066,7 +5066,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>87.65904998779297</v>
+        <v>87.6590576171875</v>
       </c>
       <c r="C182" t="n">
         <v>103.1999969482422</v>
@@ -5095,7 +5095,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>84.15099334716797</v>
+        <v>84.1510009765625</v>
       </c>
       <c r="C183" t="n">
         <v>99.06999969482422</v>
@@ -5153,7 +5153,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>99.59625244140625</v>
+        <v>99.59622955322266</v>
       </c>
       <c r="C185" t="n">
         <v>116.5299987792969</v>
@@ -5182,7 +5182,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>100.7158508300781</v>
+        <v>100.7158660888672</v>
       </c>
       <c r="C186" t="n">
         <v>117.8399963378906</v>
@@ -5269,7 +5269,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>115.6692581176758</v>
+        <v>115.6692504882812</v>
       </c>
       <c r="C189" t="n">
         <v>134.6600036621094</v>
@@ -5298,7 +5298,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>108.2525939941406</v>
+        <v>108.2526092529297</v>
       </c>
       <c r="C190" t="n">
         <v>125.4300003051758</v>
@@ -5356,7 +5356,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>130.1050720214844</v>
+        <v>130.1050567626953</v>
       </c>
       <c r="C192" t="n">
         <v>150.75</v>
@@ -5414,7 +5414,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>135.8819732666016</v>
+        <v>135.8819122314453</v>
       </c>
       <c r="C194" t="n">
         <v>156.8200073242188</v>
@@ -5443,7 +5443,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>126.3765869140625</v>
+        <v>126.376594543457</v>
       </c>
       <c r="C195" t="n">
         <v>145.8500061035156</v>
@@ -5472,7 +5472,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>140.6385345458984</v>
+        <v>140.6385192871094</v>
       </c>
       <c r="C196" t="n">
         <v>161.4799957275391</v>
@@ -5501,7 +5501,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>139.6021118164062</v>
+        <v>139.6021575927734</v>
       </c>
       <c r="C197" t="n">
         <v>160.2899932861328</v>
@@ -5530,7 +5530,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>111.026741027832</v>
+        <v>111.0267562866211</v>
       </c>
       <c r="C198" t="n">
         <v>127.4800033569336</v>
@@ -5559,7 +5559,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>103.2022399902344</v>
+        <v>103.2022094726562</v>
       </c>
       <c r="C199" t="n">
         <v>117.6500015258789</v>
@@ -5588,7 +5588,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>116.28125</v>
+        <v>116.2812271118164</v>
       </c>
       <c r="C200" t="n">
         <v>132.5599975585938</v>
@@ -5617,7 +5617,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>109.2197952270508</v>
+        <v>109.2198104858398</v>
       </c>
       <c r="C201" t="n">
         <v>124.5100021362305</v>
@@ -5646,7 +5646,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>89.68967437744141</v>
+        <v>89.68968200683594</v>
       </c>
       <c r="C202" t="n">
         <v>101.5999984741211</v>
@@ -5675,7 +5675,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>97.76704406738281</v>
+        <v>97.76705932617188</v>
       </c>
       <c r="C203" t="n">
         <v>110.75</v>
@@ -5704,7 +5704,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>103.9817810058594</v>
+        <v>103.9817733764648</v>
       </c>
       <c r="C204" t="n">
         <v>117.7900009155273</v>
@@ -5762,7 +5762,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>114.8901824951172</v>
+        <v>114.8901901245117</v>
       </c>
       <c r="C206" t="n">
         <v>129.2799987792969</v>
@@ -5820,7 +5820,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>111.6918792724609</v>
+        <v>111.6918716430664</v>
       </c>
       <c r="C208" t="n">
         <v>124.7699966430664</v>
@@ -5849,7 +5849,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>112.1215744018555</v>
+        <v>112.1215667724609</v>
       </c>
       <c r="C209" t="n">
         <v>125.25</v>
@@ -5878,7 +5878,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>111.4949340820312</v>
+        <v>111.4949493408203</v>
       </c>
       <c r="C210" t="n">
         <v>124.5500030517578</v>
@@ -5965,7 +5965,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>111.978401184082</v>
+        <v>111.978385925293</v>
       </c>
       <c r="C213" t="n">
         <v>124.1999969482422</v>
@@ -5994,7 +5994,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>101.8811492919922</v>
+        <v>101.8811645507812</v>
       </c>
       <c r="C214" t="n">
         <v>112.2099990844727</v>
@@ -6081,7 +6081,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>121.8026657104492</v>
+        <v>121.8026504516602</v>
       </c>
       <c r="C217" t="n">
         <v>133.3000030517578</v>
@@ -6139,7 +6139,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>121.775260925293</v>
+        <v>121.7752456665039</v>
       </c>
       <c r="C219" t="n">
         <v>133.2700042724609</v>
@@ -6168,7 +6168,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>119.8684310913086</v>
+        <v>119.8684158325195</v>
       </c>
       <c r="C220" t="n">
         <v>130.2200012207031</v>
@@ -6197,7 +6197,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>93.937744140625</v>
+        <v>93.93772888183594</v>
       </c>
       <c r="C221" t="n">
         <v>102.0500030517578</v>
@@ -6226,7 +6226,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>101.7068176269531</v>
+        <v>101.7068252563477</v>
       </c>
       <c r="C222" t="n">
         <v>110.4899978637695</v>
@@ -6255,7 +6255,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>104.2736053466797</v>
+        <v>104.2735900878906</v>
       </c>
       <c r="C223" t="n">
         <v>112.3099975585938</v>
@@ -6284,7 +6284,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>117.0304412841797</v>
+        <v>117.0304336547852</v>
       </c>
       <c r="C224" t="n">
         <v>126.0500030517578</v>
@@ -6313,7 +6313,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>118.6737823486328</v>
+        <v>118.6737747192383</v>
       </c>
       <c r="C225" t="n">
         <v>127.8199996948242</v>
@@ -6371,7 +6371,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>105.6387405395508</v>
+        <v>105.6387481689453</v>
       </c>
       <c r="C227" t="n">
         <v>112.9400024414062</v>
@@ -6400,7 +6400,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>109.2304916381836</v>
+        <v>109.2304992675781</v>
       </c>
       <c r="C228" t="n">
         <v>116.7799987792969</v>
@@ -6429,7 +6429,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>99.72830200195312</v>
+        <v>99.72829437255859</v>
       </c>
       <c r="C229" t="n">
         <v>105.6999969482422</v>
@@ -6487,7 +6487,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>116.9189300537109</v>
+        <v>116.9189224243164</v>
       </c>
       <c r="C231" t="n">
         <v>123.9199981689453</v>
@@ -6516,7 +6516,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>106.4134063720703</v>
+        <v>106.4133987426758</v>
       </c>
       <c r="C232" t="n">
         <v>111.7900009155273</v>
@@ -6545,7 +6545,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>97.28462982177734</v>
+        <v>97.28462219238281</v>
       </c>
       <c r="C233" t="n">
         <v>102.1999969482422</v>
@@ -6603,7 +6603,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>101.0193405151367</v>
+        <v>101.0193481445312</v>
       </c>
       <c r="C235" t="n">
         <v>105.120002746582</v>
@@ -6719,7 +6719,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>120.312744140625</v>
+        <v>120.3127517700195</v>
       </c>
       <c r="C239" t="n">
         <v>124.0899963378906</v>
@@ -6748,7 +6748,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>124.6175918579102</v>
+        <v>124.6175994873047</v>
       </c>
       <c r="C240" t="n">
         <v>128.5299987792969</v>
